--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,6 +1033,238 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128062004</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96747</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frihamra (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>698860</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6637818</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128062017</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96711</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frihamra (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698860</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6637818</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96747</v>
+        <v>96755</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96755</v>
+        <v>96756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96756</v>
+        <v>96757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96720</v>
+        <v>96721</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96757</v>
+        <v>96758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96758</v>
+        <v>96766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96722</v>
+        <v>96730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96766</v>
+        <v>96859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96730</v>
+        <v>96823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>128062004</v>
       </c>
       <c r="B5" t="n">
-        <v>96859</v>
+        <v>96871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>128062017</v>
       </c>
       <c r="B6" t="n">
-        <v>96823</v>
+        <v>96835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67607410</v>
+        <v>67607002</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,14 +709,14 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Viksjön, 600m N, Upl</t>
+          <t>Viksön, 600m N, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698754.1947377229</v>
+        <v>698762</v>
       </c>
       <c r="R2" t="n">
-        <v>6638015.177113594</v>
+        <v>6638050</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67607002</v>
+        <v>67607410</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,14 +814,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Viksön, 600m N, Upl</t>
+          <t>Viksjön, 600m N, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698761.9238858593</v>
+        <v>698754</v>
       </c>
       <c r="R3" t="n">
-        <v>6638049.843261978</v>
+        <v>6638015</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,19 +851,9 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67607097</v>
+        <v>128062017</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,39 +896,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Viksön, 600m N, Upl</t>
+          <t>Frihamra (Erken), Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698825.8532481076</v>
+        <v>698860</v>
       </c>
       <c r="R4" t="n">
-        <v>6638014.987784874</v>
+        <v>6637818</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,27 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal högvuxen tallskog med delvis inslag av olikåldrig gran. Inslag av död ved. Tidigare dikad torvmark.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +985,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128062004</v>
+        <v>67607322</v>
       </c>
       <c r="B5" t="n">
-        <v>96871</v>
+        <v>97678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,49 +1008,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2590</v>
+        <v>2326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Nees</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frihamra (Erken), Upl</t>
+          <t>Viksjön, 600m N, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698860</v>
+        <v>698894</v>
       </c>
       <c r="R5" t="n">
-        <v>6637818</v>
+        <v>6637731</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1112,22 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På rotsockel i blandsumpskog med välutvecklade rotsocklar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,51 +1084,50 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Bo Törnquist, Kjell  Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128062017</v>
+        <v>128064275</v>
       </c>
       <c r="B6" t="n">
-        <v>96835</v>
+        <v>97678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>2326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,17 +1137,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Frihamra (Erken), Upl</t>
+          <t>Erken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698860</v>
+        <v>698790</v>
       </c>
       <c r="R6" t="n">
-        <v>6637818</v>
+        <v>6637846</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,6 +1211,768 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128062004</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frihamra (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698860</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6637818</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128064276</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698790</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6637846</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67607097</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Viksön, 600m N, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698826</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6638015</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal högvuxen tallskog med delvis inslag av olikåldrig gran. Inslag av död ved. Tidigare dikad torvmark.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>67607151</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Viksjön, 600m N, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698871</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6638014</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal högvuxen tallskog med delvis inslag av olikåldrig gran. Inslag av död ved. Tidigare dikad torvmark.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67607299</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Viksjön, 600m N, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698952</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6637756</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammal högvuxen tallskog med delvis inslag av olikåldrig gran. Inslag av död ved. Tidigare dikad torvmark.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>67607345</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Viksjön, 600m N, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698893</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6637733</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran i blandsumpskog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>67607382</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Viksjön, 600m N, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698874</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6637781</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnagspår på torrgran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34524-2025 artfynd.xlsx
+++ b/artfynd/A 34524-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607002</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607410</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128062017</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607322</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128062004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064276</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607151</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607299</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607345</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,8 +2033,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67607382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>